--- a/rapporten/prijsrapport-2026-04-11.xlsx
+++ b/rapporten/prijsrapport-2026-04-11.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="109">
   <si>
     <t>Product</t>
   </si>
@@ -37,10 +37,10 @@
     <t>Fulfilment</t>
   </si>
   <si>
-    <t>Hello Kitty - Giftset - Sweet Leopard Pink - Eau de Parfum + Bodymist - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>8721055496373</t>
+    <t>Creation Lamis Ruler Giftset</t>
+  </si>
+  <si>
+    <t>6291012002678</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
@@ -49,28 +49,19 @@
     <t>FBR</t>
   </si>
   <si>
-    <t>Creation Lamis Ruler Giftset</t>
-  </si>
-  <si>
-    <t>6291012002678</t>
-  </si>
-  <si>
-    <t>Hello Kitty - Giftset - Delicate Flower - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>7640158816950</t>
-  </si>
-  <si>
-    <t>Creation Lamis Paraverse 100ml Eau de Parfum for women</t>
-  </si>
-  <si>
-    <t>6291012005082</t>
-  </si>
-  <si>
     <t>Creation Lamis Catsuit Woman Eau de Parfum For Women 100 ml</t>
   </si>
   <si>
     <t>6151010029070</t>
+  </si>
+  <si>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
+    <t>5414666014427</t>
+  </si>
+  <si>
+    <t>Juwelium</t>
   </si>
   <si>
     <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
@@ -738,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -785,19 +776,19 @@
         <v>9</v>
       </c>
       <c r="C2" s="1">
-        <v>16.95</v>
+        <v>14.99</v>
       </c>
       <c r="D2" s="1">
-        <v>15.63</v>
+        <v>13.87</v>
       </c>
       <c r="E2" s="1">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>15.63</v>
+        <v>13.87</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -811,19 +802,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>14.99</v>
+        <v>13.59</v>
       </c>
       <c r="D3" s="1">
-        <v>13.87</v>
+        <v>13.06</v>
       </c>
       <c r="E3" s="1">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>13.87</v>
+        <v>13.06</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -837,19 +828,19 @@
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>15.95</v>
+        <v>9.95</v>
       </c>
       <c r="D4" s="1">
-        <v>15.14</v>
+        <v>9.48</v>
       </c>
       <c r="E4" s="1">
-        <v>0.81</v>
+        <v>0.47</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1">
-        <v>15.14</v>
+        <v>9.48</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -857,25 +848,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
-        <v>15.15</v>
+        <v>5.25</v>
       </c>
       <c r="D5" s="1">
-        <v>14.81</v>
+        <v>4.99</v>
       </c>
       <c r="E5" s="1">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
-        <v>14.81</v>
+        <v>4.99</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -883,25 +874,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="D6" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="F6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1">
-        <v>13.95</v>
-      </c>
-      <c r="D6" s="1">
-        <v>13.63</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
       <c r="G6" s="1">
-        <v>13.63</v>
+        <v>4.99</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -909,10 +900,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
         <v>5.25</v>
@@ -924,7 +915,7 @@
         <v>0.26</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G7" s="1">
         <v>4.99</v>
@@ -935,10 +926,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1">
         <v>5.25</v>
@@ -950,7 +941,7 @@
         <v>0.26</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1">
         <v>4.99</v>
@@ -961,10 +952,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1">
         <v>5.25</v>
@@ -976,7 +967,7 @@
         <v>0.26</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G9" s="1">
         <v>4.99</v>
@@ -987,10 +978,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>5.25</v>
@@ -1002,7 +993,7 @@
         <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
         <v>4.99</v>
@@ -1013,10 +1004,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1">
         <v>5.25</v>
@@ -1028,7 +1019,7 @@
         <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1">
         <v>4.99</v>
@@ -1039,10 +1030,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>5.25</v>
@@ -1054,7 +1045,7 @@
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
@@ -1065,10 +1056,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1">
         <v>5.25</v>
@@ -1080,7 +1071,7 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
@@ -1091,10 +1082,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1">
         <v>5.25</v>
@@ -1106,7 +1097,7 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
@@ -1117,10 +1108,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1">
         <v>5.25</v>
@@ -1132,7 +1123,7 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
@@ -1143,10 +1134,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1">
         <v>5.25</v>
@@ -1158,7 +1149,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
@@ -1169,10 +1160,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1">
         <v>5.25</v>
@@ -1184,7 +1175,7 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
@@ -1195,10 +1186,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1">
         <v>5.25</v>
@@ -1210,7 +1201,7 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
@@ -1221,10 +1212,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1">
         <v>5.25</v>
@@ -1236,7 +1227,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1247,10 +1238,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1">
         <v>5.25</v>
@@ -1262,7 +1253,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1273,10 +1264,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1">
         <v>5.25</v>
@@ -1288,7 +1279,7 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
@@ -1299,10 +1290,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1">
         <v>5.25</v>
@@ -1314,7 +1305,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1325,25 +1316,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D23" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E23" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F23" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="G23" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -1351,25 +1342,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1">
-        <v>5.25</v>
+        <v>9.99</v>
       </c>
       <c r="D24" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E24" s="1">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F24" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="G24" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
@@ -1377,25 +1368,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C25" s="1">
-        <v>9.99</v>
+        <v>5.19</v>
       </c>
       <c r="D25" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E25" s="1">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="G25" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
@@ -1403,25 +1394,25 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="1">
-        <v>9.99</v>
+        <v>5.19</v>
       </c>
       <c r="D26" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E26" s="1">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="G26" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
@@ -1429,10 +1420,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1">
         <v>5.19</v>
@@ -1444,7 +1435,7 @@
         <v>0.2</v>
       </c>
       <c r="F27" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G27" s="1">
         <v>4.99</v>
@@ -1455,25 +1446,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1">
-        <v>5.19</v>
+        <v>13.75</v>
       </c>
       <c r="D28" s="1">
-        <v>4.99</v>
+        <v>13.56</v>
       </c>
       <c r="E28" s="1">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F28" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G28" s="1">
-        <v>4.99</v>
+        <v>13.56</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
@@ -1481,25 +1472,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1">
-        <v>5.19</v>
+        <v>9.99</v>
       </c>
       <c r="D29" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E29" s="1">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="F29" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="G29" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
@@ -1507,25 +1498,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1">
-        <v>13.75</v>
+        <v>9.99</v>
       </c>
       <c r="D30" s="1">
-        <v>13.56</v>
+        <v>9.95</v>
       </c>
       <c r="E30" s="1">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="G30" s="1">
-        <v>13.56</v>
+        <v>9.95</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -1533,10 +1524,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1">
         <v>9.99</v>
@@ -1548,7 +1539,7 @@
         <v>0.04</v>
       </c>
       <c r="F31" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G31" s="1">
         <v>9.95</v>
@@ -1559,10 +1550,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1">
         <v>9.99</v>
@@ -1574,7 +1565,7 @@
         <v>0.04</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G32" s="1">
         <v>9.95</v>
@@ -1585,10 +1576,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1">
         <v>9.99</v>
@@ -1600,7 +1591,7 @@
         <v>0.04</v>
       </c>
       <c r="F33" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G33" s="1">
         <v>9.95</v>
@@ -1611,10 +1602,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1">
         <v>9.99</v>
@@ -1626,7 +1617,7 @@
         <v>0.04</v>
       </c>
       <c r="F34" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G34" s="1">
         <v>9.95</v>
@@ -1637,10 +1628,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1">
         <v>9.99</v>
@@ -1652,7 +1643,7 @@
         <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G35" s="1">
         <v>9.95</v>
@@ -1663,10 +1654,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1">
         <v>9.99</v>
@@ -1678,7 +1669,7 @@
         <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G36" s="1">
         <v>9.95</v>
@@ -1689,10 +1680,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" s="1">
         <v>9.99</v>
@@ -1704,7 +1695,7 @@
         <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G37" s="1">
         <v>9.95</v>
@@ -1715,10 +1706,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1">
         <v>9.99</v>
@@ -1730,7 +1721,7 @@
         <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G38" s="1">
         <v>9.95</v>
@@ -1741,10 +1732,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1">
         <v>9.99</v>
@@ -1756,7 +1747,7 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
@@ -1767,10 +1758,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="1">
         <v>9.99</v>
@@ -1782,7 +1773,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
@@ -1793,10 +1784,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" s="1">
         <v>9.99</v>
@@ -1808,7 +1799,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1819,10 +1810,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" s="1">
         <v>9.99</v>
@@ -1834,7 +1825,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1845,10 +1836,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" s="1">
         <v>9.99</v>
@@ -1860,7 +1851,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1871,10 +1862,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1">
         <v>9.99</v>
@@ -1886,7 +1877,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1897,10 +1888,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1">
         <v>9.99</v>
@@ -1912,7 +1903,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -1923,10 +1914,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C46" s="1">
         <v>9.99</v>
@@ -1938,7 +1929,7 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
@@ -1949,10 +1940,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C47" s="1">
         <v>9.99</v>
@@ -1964,7 +1955,7 @@
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G47" s="1">
         <v>9.95</v>
@@ -1975,10 +1966,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C48" s="1">
         <v>9.99</v>
@@ -1990,7 +1981,7 @@
         <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G48" s="1">
         <v>9.95</v>
@@ -2001,10 +1992,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C49" s="1">
         <v>9.99</v>
@@ -2016,64 +2007,12 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
       </c>
       <c r="H49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>108</v>
-      </c>
-      <c r="B50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D50" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E50" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F50" t="s">
-        <v>59</v>
-      </c>
-      <c r="G50" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>110</v>
-      </c>
-      <c r="B51" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D51" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E51" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F51" t="s">
-        <v>59</v>
-      </c>
-      <c r="G51" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H51" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-04-11.xlsx
+++ b/rapporten/prijsrapport-2026-04-11.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="111">
   <si>
     <t>Product</t>
   </si>
@@ -47,6 +47,12 @@
   </si>
   <si>
     <t>FBR</t>
+  </si>
+  <si>
+    <t>Omerta - Fair Fight - Eau De Toilette - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658997924</t>
   </si>
   <si>
     <t>Creation Lamis Catsuit Woman Eau de Parfum For Women 100 ml</t>
@@ -729,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -802,19 +808,19 @@
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>13.59</v>
+        <v>13.75</v>
       </c>
       <c r="D3" s="1">
-        <v>13.06</v>
+        <v>13.16</v>
       </c>
       <c r="E3" s="1">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>13.06</v>
+        <v>13.16</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -828,19 +834,19 @@
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>9.95</v>
+        <v>13.59</v>
       </c>
       <c r="D4" s="1">
-        <v>9.48</v>
+        <v>13.06</v>
       </c>
       <c r="E4" s="1">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>9.48</v>
+        <v>13.06</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -848,25 +854,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="D5" s="1">
+        <v>9.48</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="1">
-        <v>5.25</v>
-      </c>
-      <c r="D5" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
       <c r="G5" s="1">
-        <v>4.99</v>
+        <v>9.48</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -874,10 +880,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
       </c>
       <c r="C6" s="1">
         <v>5.25</v>
@@ -889,7 +895,7 @@
         <v>0.26</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1">
         <v>4.99</v>
@@ -915,7 +921,7 @@
         <v>0.26</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1">
         <v>4.99</v>
@@ -941,7 +947,7 @@
         <v>0.26</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" s="1">
         <v>4.99</v>
@@ -967,7 +973,7 @@
         <v>0.26</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="1">
         <v>4.99</v>
@@ -993,7 +999,7 @@
         <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G10" s="1">
         <v>4.99</v>
@@ -1019,7 +1025,7 @@
         <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G11" s="1">
         <v>4.99</v>
@@ -1045,7 +1051,7 @@
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
@@ -1071,7 +1077,7 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
@@ -1097,7 +1103,7 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
@@ -1123,7 +1129,7 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
@@ -1149,7 +1155,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
@@ -1175,7 +1181,7 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
@@ -1201,7 +1207,7 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
@@ -1227,7 +1233,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1253,7 +1259,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1279,7 +1285,7 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
@@ -1305,7 +1311,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1322,19 +1328,19 @@
         <v>55</v>
       </c>
       <c r="C23" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D23" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E23" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="G23" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -1342,10 +1348,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" t="s">
         <v>57</v>
-      </c>
-      <c r="B24" t="s">
-        <v>58</v>
       </c>
       <c r="C24" s="1">
         <v>9.99</v>
@@ -1357,7 +1363,7 @@
         <v>0.24</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G24" s="1">
         <v>9.75</v>
@@ -1374,19 +1380,19 @@
         <v>60</v>
       </c>
       <c r="C25" s="1">
-        <v>5.19</v>
+        <v>9.99</v>
       </c>
       <c r="D25" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E25" s="1">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="G25" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
@@ -1409,7 +1415,7 @@
         <v>0.2</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G26" s="1">
         <v>4.99</v>
@@ -1435,7 +1441,7 @@
         <v>0.2</v>
       </c>
       <c r="F27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G27" s="1">
         <v>4.99</v>
@@ -1452,19 +1458,19 @@
         <v>66</v>
       </c>
       <c r="C28" s="1">
-        <v>13.75</v>
+        <v>5.19</v>
       </c>
       <c r="D28" s="1">
-        <v>13.56</v>
+        <v>4.99</v>
       </c>
       <c r="E28" s="1">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G28" s="1">
-        <v>13.56</v>
+        <v>4.99</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
@@ -1478,19 +1484,19 @@
         <v>68</v>
       </c>
       <c r="C29" s="1">
-        <v>9.99</v>
+        <v>13.75</v>
       </c>
       <c r="D29" s="1">
-        <v>9.95</v>
+        <v>13.56</v>
       </c>
       <c r="E29" s="1">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="G29" s="1">
-        <v>9.95</v>
+        <v>13.56</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
@@ -1513,7 +1519,7 @@
         <v>0.04</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G30" s="1">
         <v>9.95</v>
@@ -1539,7 +1545,7 @@
         <v>0.04</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G31" s="1">
         <v>9.95</v>
@@ -1565,7 +1571,7 @@
         <v>0.04</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G32" s="1">
         <v>9.95</v>
@@ -1591,7 +1597,7 @@
         <v>0.04</v>
       </c>
       <c r="F33" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G33" s="1">
         <v>9.95</v>
@@ -1617,7 +1623,7 @@
         <v>0.04</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G34" s="1">
         <v>9.95</v>
@@ -1643,7 +1649,7 @@
         <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G35" s="1">
         <v>9.95</v>
@@ -1669,7 +1675,7 @@
         <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G36" s="1">
         <v>9.95</v>
@@ -1695,7 +1701,7 @@
         <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G37" s="1">
         <v>9.95</v>
@@ -1721,7 +1727,7 @@
         <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G38" s="1">
         <v>9.95</v>
@@ -1747,7 +1753,7 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
@@ -1773,7 +1779,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
@@ -1799,7 +1805,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1825,7 +1831,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1851,7 +1857,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1877,7 +1883,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1903,7 +1909,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -1929,7 +1935,7 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
@@ -1955,7 +1961,7 @@
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G47" s="1">
         <v>9.95</v>
@@ -1981,7 +1987,7 @@
         <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G48" s="1">
         <v>9.95</v>
@@ -2007,12 +2013,38 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
       </c>
       <c r="H49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D50" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F50" t="s">
+        <v>58</v>
+      </c>
+      <c r="G50" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H50" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-04-11.xlsx
+++ b/rapporten/prijsrapport-2026-04-11.xlsx
@@ -49,16 +49,10 @@
     <t>FBR</t>
   </si>
   <si>
-    <t>Omerta - Fair Fight - Eau De Toilette - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658997924</t>
-  </si>
-  <si>
-    <t>Creation Lamis Catsuit Woman Eau de Parfum For Women 100 ml</t>
-  </si>
-  <si>
-    <t>6151010029070</t>
+    <t>Omerta - Vanilla Fun - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658999447</t>
   </si>
   <si>
     <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
@@ -103,6 +97,12 @@
     <t>7640158816677</t>
   </si>
   <si>
+    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816653</t>
+  </si>
+  <si>
     <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
   </si>
   <si>
@@ -121,6 +121,12 @@
     <t>8721055493891</t>
   </si>
   <si>
+    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816714</t>
+  </si>
+  <si>
     <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
   </si>
   <si>
@@ -139,6 +145,12 @@
     <t>7640158816790</t>
   </si>
   <si>
+    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>7640158816639</t>
+  </si>
+  <si>
     <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
   </si>
   <si>
@@ -196,28 +208,16 @@
     <t>8715658370062</t>
   </si>
   <si>
-    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816653</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816714</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816639</t>
-  </si>
-  <si>
-    <t>Vibezz Astrolux parfum - Eau de parfum voor haar - 100ml</t>
-  </si>
-  <si>
-    <t>7640158819173</t>
+    <t>Sentio Happy Holidays Pink parfum - Eau de parfum in kerstbal - 30ml</t>
+  </si>
+  <si>
+    <t>8721055493068</t>
+  </si>
+  <si>
+    <t>Street Looks - Pure Courage - Eau de Toilette - 100ML</t>
+  </si>
+  <si>
+    <t>8715658013082</t>
   </si>
   <si>
     <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
@@ -811,16 +811,16 @@
         <v>13.75</v>
       </c>
       <c r="D3" s="1">
-        <v>13.16</v>
+        <v>13.07</v>
       </c>
       <c r="E3" s="1">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>13.16</v>
+        <v>13.07</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -834,19 +834,19 @@
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>13.59</v>
+        <v>9.95</v>
       </c>
       <c r="D4" s="1">
-        <v>13.06</v>
+        <v>9.48</v>
       </c>
       <c r="E4" s="1">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1">
-        <v>13.06</v>
+        <v>9.48</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -854,25 +854,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
-        <v>9.95</v>
+        <v>5.25</v>
       </c>
       <c r="D5" s="1">
-        <v>9.48</v>
+        <v>4.99</v>
       </c>
       <c r="E5" s="1">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
-        <v>9.48</v>
+        <v>4.99</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
         <v>5.25</v>
@@ -895,7 +895,7 @@
         <v>0.26</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1">
         <v>4.99</v>
@@ -921,7 +921,7 @@
         <v>0.26</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G7" s="1">
         <v>4.99</v>
@@ -947,7 +947,7 @@
         <v>0.26</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1">
         <v>4.99</v>
@@ -973,7 +973,7 @@
         <v>0.26</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G9" s="1">
         <v>4.99</v>
@@ -999,7 +999,7 @@
         <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1">
         <v>4.99</v>
@@ -1025,7 +1025,7 @@
         <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1">
         <v>4.99</v>
@@ -1051,7 +1051,7 @@
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
@@ -1077,7 +1077,7 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
@@ -1103,7 +1103,7 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
@@ -1129,7 +1129,7 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
@@ -1155,7 +1155,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
@@ -1181,7 +1181,7 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
@@ -1207,7 +1207,7 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
@@ -1233,7 +1233,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1259,7 +1259,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1285,7 +1285,7 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
@@ -1311,7 +1311,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1337,7 +1337,7 @@
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
@@ -1354,19 +1354,19 @@
         <v>57</v>
       </c>
       <c r="C24" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D24" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E24" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
@@ -1374,25 +1374,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" t="s">
         <v>59</v>
       </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
       <c r="C25" s="1">
-        <v>9.99</v>
+        <v>5.25</v>
       </c>
       <c r="D25" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="E25" s="1">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="G25" s="1">
-        <v>9.75</v>
+        <v>4.99</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
@@ -1400,25 +1400,25 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
         <v>61</v>
       </c>
-      <c r="B26" t="s">
-        <v>62</v>
-      </c>
       <c r="C26" s="1">
-        <v>5.19</v>
+        <v>9.99</v>
       </c>
       <c r="D26" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E26" s="1">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G26" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
@@ -1432,19 +1432,19 @@
         <v>64</v>
       </c>
       <c r="C27" s="1">
-        <v>5.19</v>
+        <v>9.99</v>
       </c>
       <c r="D27" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="E27" s="1">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G27" s="1">
-        <v>4.99</v>
+        <v>9.75</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
@@ -1458,19 +1458,19 @@
         <v>66</v>
       </c>
       <c r="C28" s="1">
-        <v>5.19</v>
+        <v>12.25</v>
       </c>
       <c r="D28" s="1">
-        <v>4.99</v>
+        <v>12.06</v>
       </c>
       <c r="E28" s="1">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G28" s="1">
-        <v>4.99</v>
+        <v>12.06</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
@@ -1519,7 +1519,7 @@
         <v>0.04</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G30" s="1">
         <v>9.95</v>
@@ -1545,7 +1545,7 @@
         <v>0.04</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G31" s="1">
         <v>9.95</v>
@@ -1571,7 +1571,7 @@
         <v>0.04</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G32" s="1">
         <v>9.95</v>
@@ -1597,7 +1597,7 @@
         <v>0.04</v>
       </c>
       <c r="F33" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G33" s="1">
         <v>9.95</v>
@@ -1623,7 +1623,7 @@
         <v>0.04</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G34" s="1">
         <v>9.95</v>
@@ -1649,7 +1649,7 @@
         <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G35" s="1">
         <v>9.95</v>
@@ -1675,7 +1675,7 @@
         <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G36" s="1">
         <v>9.95</v>
@@ -1701,7 +1701,7 @@
         <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G37" s="1">
         <v>9.95</v>
@@ -1727,7 +1727,7 @@
         <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G38" s="1">
         <v>9.95</v>
@@ -1753,7 +1753,7 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
@@ -1779,7 +1779,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
@@ -1805,7 +1805,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1831,7 +1831,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1857,7 +1857,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1883,7 +1883,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1909,7 +1909,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -1935,7 +1935,7 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
@@ -1961,7 +1961,7 @@
         <v>0.04</v>
       </c>
       <c r="F47" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G47" s="1">
         <v>9.95</v>
@@ -1987,7 +1987,7 @@
         <v>0.04</v>
       </c>
       <c r="F48" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G48" s="1">
         <v>9.95</v>
@@ -2013,7 +2013,7 @@
         <v>0.04</v>
       </c>
       <c r="F49" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G49" s="1">
         <v>9.95</v>
@@ -2039,7 +2039,7 @@
         <v>0.04</v>
       </c>
       <c r="F50" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G50" s="1">
         <v>9.95</v>

--- a/rapporten/prijsrapport-2026-04-11.xlsx
+++ b/rapporten/prijsrapport-2026-04-11.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="58">
   <si>
     <t>Product</t>
   </si>
@@ -37,310 +37,151 @@
     <t>Fulfilment</t>
   </si>
   <si>
-    <t>Creation Lamis Ruler Giftset</t>
-  </si>
-  <si>
     <t>6291012002678</t>
   </si>
   <si>
-    <t>Koopjesfun.nl</t>
+    <t>1762224</t>
   </si>
   <si>
     <t>FBR</t>
   </si>
   <si>
-    <t>Omerta - Fair Fight - Eau De Toilette - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658997924</t>
-  </si>
-  <si>
-    <t>Creation Lamis Catsuit Woman Eau de Parfum For Women 100 ml</t>
-  </si>
-  <si>
-    <t>6151010029070</t>
-  </si>
-  <si>
-    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
-  </si>
-  <si>
     <t>5414666014427</t>
   </si>
   <si>
-    <t>Juwelium</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+    <t>1692530</t>
+  </si>
+  <si>
+    <t>6291012005648</t>
+  </si>
+  <si>
+    <t>8721055493860</t>
+  </si>
+  <si>
+    <t>946246</t>
   </si>
   <si>
     <t>8721055494225</t>
   </si>
   <si>
-    <t>Minimarkt W&amp;M</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Discover - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
-    <t>8721055493860</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
     <t>8721055494263</t>
   </si>
   <si>
-    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
-  </si>
-  <si>
     <t>7640158816691</t>
   </si>
   <si>
-    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
-  </si>
-  <si>
     <t>7640158816677</t>
   </si>
   <si>
-    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+    <t>7640158816653</t>
   </si>
   <si>
     <t>8721055494270</t>
   </si>
   <si>
-    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
-  </si>
-  <si>
     <t>8721055494232</t>
   </si>
   <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Sparkle- Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
     <t>8721055493891</t>
   </si>
   <si>
-    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
-  </si>
-  <si>
     <t>7640158816615</t>
   </si>
   <si>
-    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
-  </si>
-  <si>
     <t>8721055493211</t>
   </si>
   <si>
-    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
-  </si>
-  <si>
     <t>7640158816790</t>
   </si>
   <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Embrace - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
     <t>8721055493884</t>
   </si>
   <si>
-    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
-  </si>
-  <si>
     <t>7640158816837</t>
   </si>
   <si>
-    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
-  </si>
-  <si>
     <t>7640158816813</t>
   </si>
   <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Smile - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
     <t>8721055493853</t>
   </si>
   <si>
-    <t>Bubble Bliss - Unicorn Sprinkles - Shine - Lika a Unicorn - eau de parfum - voor kinderen 15ml</t>
-  </si>
-  <si>
     <t>8721055493877</t>
   </si>
   <si>
-    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
-  </si>
-  <si>
     <t>8721055493198</t>
   </si>
   <si>
-    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
-  </si>
-  <si>
     <t>8721055493228</t>
   </si>
   <si>
-    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370505</t>
-  </si>
-  <si>
-    <t>Bliksma Retail B.V.</t>
-  </si>
-  <si>
-    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>8715658370062</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816653</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816714</t>
-  </si>
-  <si>
-    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
-  </si>
-  <si>
-    <t>7640158816639</t>
-  </si>
-  <si>
-    <t>Vibezz Astrolux parfum - Eau de parfum voor haar - 100ml</t>
-  </si>
-  <si>
-    <t>7640158819173</t>
-  </si>
-  <si>
-    <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
+    <t>8721055493068</t>
+  </si>
+  <si>
+    <t>8715658013082</t>
   </si>
   <si>
     <t>8715658380931</t>
   </si>
   <si>
-    <t>Omerta Love Feathers - Eau de parfum - 100ML</t>
+    <t>1840300</t>
   </si>
   <si>
     <t>8715658999430</t>
   </si>
   <si>
-    <t>Omerta - Big Release The Mood - EDT men - 100ml</t>
-  </si>
-  <si>
     <t>8715658370086</t>
   </si>
   <si>
-    <t>Omerta - Golden challenge EDT men 100 ml</t>
-  </si>
-  <si>
     <t>8720938379345</t>
   </si>
   <si>
-    <t>Omerta - Invasion - Eau De Parfum - 100Ml</t>
-  </si>
-  <si>
     <t>8715658380351</t>
   </si>
   <si>
-    <t>Omerta - Oh So Black For Women - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
     <t>8715658380221</t>
   </si>
   <si>
-    <t>Omerta - Twice so nice - Eau de parfum - 100ml</t>
-  </si>
-  <si>
     <t>8720938379352</t>
   </si>
   <si>
-    <t>Omerta -Royal X Red- 100ml Eau de Toilette for men</t>
-  </si>
-  <si>
     <t>8715658370369</t>
   </si>
   <si>
-    <t>Omerta Clouds of Love Eau de Parfum 100ml</t>
-  </si>
-  <si>
     <t>8715658999638</t>
   </si>
   <si>
-    <t>Omerta - Conclude Oud Extreme Attraction - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
     <t>8715658370543</t>
   </si>
   <si>
-    <t>Omerta -Ladies World- Eau de Parfum 100ml</t>
-  </si>
-  <si>
     <t>8715658380757</t>
   </si>
   <si>
-    <t>Omerta -Lazy Nights- Eau de Parfum 100ml</t>
-  </si>
-  <si>
     <t>8715658380405</t>
   </si>
   <si>
-    <t>Omerta -Shoe Red- Eau de Parfum 100ml</t>
-  </si>
-  <si>
     <t>8715658380672</t>
   </si>
   <si>
-    <t>Omerta Sensible Man 100ml Eau de Toilette</t>
-  </si>
-  <si>
     <t>8715658999249</t>
   </si>
   <si>
-    <t>Omerta - Love Dust - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
     <t>8715658380115</t>
   </si>
   <si>
-    <t>Omerta - Express Sensualite Energy - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
     <t>8715658998839</t>
   </si>
   <si>
-    <t>Omerta - Golden Challenge Ladies World - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
     <t>8715658997993</t>
   </si>
   <si>
-    <t>Omerta -Shoe Blue- Eau de Parfum 100ml</t>
-  </si>
-  <si>
     <t>8715658380665</t>
   </si>
   <si>
-    <t>Omerta -Golden Challenge Elixer- 100ml Eau de Toilette for men</t>
-  </si>
-  <si>
     <t>8715658370437</t>
   </si>
   <si>
-    <t>Omerta Invasion Awakening - Vrouwelijke eau de parfum - 100ml</t>
-  </si>
-  <si>
     <t>8715658380658</t>
-  </si>
-  <si>
-    <t>Omerta - La Donna X - Eau De Parfum - for women - 100ML</t>
   </si>
   <si>
     <t>8715658380580</t>
@@ -735,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -779,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1">
         <v>14.99</v>
@@ -791,99 +632,99 @@
         <v>1.12</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
         <v>13.87</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="D3" s="1">
+        <v>9.48</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1">
-        <v>13.75</v>
-      </c>
-      <c r="D3" s="1">
-        <v>13.16</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
       <c r="G3" s="1">
-        <v>13.16</v>
+        <v>9.48</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1">
-        <v>13.59</v>
+        <v>15.95</v>
       </c>
       <c r="D4" s="1">
-        <v>13.06</v>
+        <v>15.56</v>
       </c>
       <c r="E4" s="1">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>13.06</v>
+        <v>15.56</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1">
-        <v>9.95</v>
+        <v>5.25</v>
       </c>
       <c r="D5" s="1">
-        <v>9.48</v>
+        <v>4.99</v>
       </c>
       <c r="E5" s="1">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1">
-        <v>9.48</v>
+        <v>4.99</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1">
         <v>5.25</v>
@@ -895,21 +736,21 @@
         <v>0.26</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1">
         <v>4.99</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1">
         <v>5.25</v>
@@ -921,21 +762,21 @@
         <v>0.26</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
         <v>4.99</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1">
         <v>5.25</v>
@@ -947,21 +788,21 @@
         <v>0.26</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
         <v>4.99</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1">
         <v>5.25</v>
@@ -973,21 +814,21 @@
         <v>0.26</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G9" s="1">
         <v>4.99</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1">
         <v>5.25</v>
@@ -999,21 +840,21 @@
         <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1">
         <v>4.99</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C11" s="1">
         <v>5.25</v>
@@ -1025,21 +866,21 @@
         <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G11" s="1">
         <v>4.99</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1">
         <v>5.25</v>
@@ -1051,21 +892,21 @@
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1">
         <v>5.25</v>
@@ -1077,21 +918,21 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
       </c>
       <c r="H13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1">
         <v>5.25</v>
@@ -1103,21 +944,21 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
       </c>
       <c r="H14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1">
         <v>5.25</v>
@@ -1129,21 +970,21 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C16" s="1">
         <v>5.25</v>
@@ -1155,21 +996,21 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
       </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1">
         <v>5.25</v>
@@ -1181,21 +1022,21 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
       </c>
       <c r="H17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1">
         <v>5.25</v>
@@ -1207,21 +1048,21 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
       </c>
       <c r="H18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C19" s="1">
         <v>5.25</v>
@@ -1233,21 +1074,21 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1">
         <v>5.25</v>
@@ -1259,21 +1100,21 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
       </c>
       <c r="H20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C21" s="1">
         <v>5.25</v>
@@ -1285,21 +1126,21 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C22" s="1">
         <v>5.25</v>
@@ -1311,21 +1152,21 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
       </c>
       <c r="H22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1">
         <v>5.25</v>
@@ -1337,177 +1178,177 @@
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="C24" s="1">
-        <v>9.99</v>
+        <v>12.25</v>
       </c>
       <c r="D24" s="1">
-        <v>9.75</v>
+        <v>12.06</v>
       </c>
       <c r="E24" s="1">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="G24" s="1">
-        <v>9.75</v>
+        <v>12.06</v>
       </c>
       <c r="H24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C25" s="1">
-        <v>9.99</v>
+        <v>13.75</v>
       </c>
       <c r="D25" s="1">
-        <v>9.75</v>
+        <v>13.56</v>
       </c>
       <c r="E25" s="1">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="G25" s="1">
-        <v>9.75</v>
+        <v>13.56</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C26" s="1">
-        <v>5.19</v>
+        <v>9.99</v>
       </c>
       <c r="D26" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E26" s="1">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G26" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C27" s="1">
-        <v>5.19</v>
+        <v>9.99</v>
       </c>
       <c r="D27" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E27" s="1">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G27" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C28" s="1">
-        <v>5.19</v>
+        <v>9.99</v>
       </c>
       <c r="D28" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="E28" s="1">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G28" s="1">
-        <v>4.99</v>
+        <v>9.95</v>
       </c>
       <c r="H28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C29" s="1">
-        <v>13.75</v>
+        <v>9.99</v>
       </c>
       <c r="D29" s="1">
-        <v>13.56</v>
+        <v>9.95</v>
       </c>
       <c r="E29" s="1">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G29" s="1">
-        <v>13.56</v>
+        <v>9.95</v>
       </c>
       <c r="H29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="C30" s="1">
         <v>9.99</v>
@@ -1519,21 +1360,21 @@
         <v>0.04</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G30" s="1">
         <v>9.95</v>
       </c>
       <c r="H30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C31" s="1">
         <v>9.99</v>
@@ -1545,21 +1386,21 @@
         <v>0.04</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G31" s="1">
         <v>9.95</v>
       </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C32" s="1">
         <v>9.99</v>
@@ -1571,21 +1412,21 @@
         <v>0.04</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G32" s="1">
         <v>9.95</v>
       </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C33" s="1">
         <v>9.99</v>
@@ -1597,21 +1438,21 @@
         <v>0.04</v>
       </c>
       <c r="F33" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G33" s="1">
         <v>9.95</v>
       </c>
       <c r="H33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C34" s="1">
         <v>9.99</v>
@@ -1623,21 +1464,21 @@
         <v>0.04</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G34" s="1">
         <v>9.95</v>
       </c>
       <c r="H34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C35" s="1">
         <v>9.99</v>
@@ -1649,21 +1490,21 @@
         <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G35" s="1">
         <v>9.95</v>
       </c>
       <c r="H35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="C36" s="1">
         <v>9.99</v>
@@ -1675,21 +1516,21 @@
         <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G36" s="1">
         <v>9.95</v>
       </c>
       <c r="H36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C37" s="1">
         <v>9.99</v>
@@ -1701,21 +1542,21 @@
         <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G37" s="1">
         <v>9.95</v>
       </c>
       <c r="H37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="C38" s="1">
         <v>9.99</v>
@@ -1727,21 +1568,21 @@
         <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G38" s="1">
         <v>9.95</v>
       </c>
       <c r="H38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C39" s="1">
         <v>9.99</v>
@@ -1753,21 +1594,21 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
       </c>
       <c r="H39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="C40" s="1">
         <v>9.99</v>
@@ -1779,21 +1620,21 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
       </c>
       <c r="H40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C41" s="1">
         <v>9.99</v>
@@ -1805,21 +1646,21 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
       </c>
       <c r="H41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="C42" s="1">
         <v>9.99</v>
@@ -1831,21 +1672,21 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
       </c>
       <c r="H42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="C43" s="1">
         <v>9.99</v>
@@ -1857,21 +1698,21 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
       </c>
       <c r="H43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="C44" s="1">
         <v>9.99</v>
@@ -1883,21 +1724,21 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
       </c>
       <c r="H44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="C45" s="1">
         <v>9.99</v>
@@ -1909,21 +1750,21 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
       </c>
       <c r="H45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="C46" s="1">
         <v>9.99</v>
@@ -1935,117 +1776,13 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
       </c>
       <c r="H46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>103</v>
-      </c>
-      <c r="B47" t="s">
-        <v>104</v>
-      </c>
-      <c r="C47" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D47" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E47" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F47" t="s">
-        <v>58</v>
-      </c>
-      <c r="G47" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" t="s">
-        <v>106</v>
-      </c>
-      <c r="C48" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D48" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E48" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-      <c r="G48" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>107</v>
-      </c>
-      <c r="B49" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D49" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E49" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-      <c r="G49" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>109</v>
-      </c>
-      <c r="B50" t="s">
-        <v>110</v>
-      </c>
-      <c r="C50" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="D50" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="E50" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F50" t="s">
-        <v>58</v>
-      </c>
-      <c r="G50" s="1">
-        <v>9.95</v>
-      </c>
-      <c r="H50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/prijsrapport-2026-04-11.xlsx
+++ b/rapporten/prijsrapport-2026-04-11.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="60">
   <si>
     <t>Product</t>
   </si>
@@ -46,13 +46,19 @@
     <t>FBR</t>
   </si>
   <si>
+    <t>8721055494126</t>
+  </si>
+  <si>
     <t>5414666014427</t>
   </si>
   <si>
     <t>1692530</t>
   </si>
   <si>
-    <t>6291012005648</t>
+    <t>8715658013082</t>
+  </si>
+  <si>
+    <t>5414666010511</t>
   </si>
   <si>
     <t>8721055493860</t>
@@ -118,7 +124,7 @@
     <t>8721055493068</t>
   </si>
   <si>
-    <t>8715658013082</t>
+    <t>8715658008354</t>
   </si>
   <si>
     <t>8715658380931</t>
@@ -576,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -649,19 +655,19 @@
         <v>11</v>
       </c>
       <c r="C3" s="1">
-        <v>9.95</v>
+        <v>13.79</v>
       </c>
       <c r="D3" s="1">
-        <v>9.48</v>
+        <v>13.07</v>
       </c>
       <c r="E3" s="1">
-        <v>0.47</v>
+        <v>0.72</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>9.48</v>
+        <v>13.07</v>
       </c>
       <c r="H3" t="s">
         <v>10</v>
@@ -669,25 +675,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="D4" s="1">
+        <v>9.48</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1">
-        <v>15.95</v>
-      </c>
-      <c r="D4" s="1">
-        <v>15.56</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
       <c r="G4" s="1">
-        <v>15.56</v>
+        <v>9.48</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
@@ -701,19 +707,19 @@
         <v>14</v>
       </c>
       <c r="C5" s="1">
-        <v>5.25</v>
+        <v>13.75</v>
       </c>
       <c r="D5" s="1">
-        <v>4.99</v>
+        <v>13.35</v>
       </c>
       <c r="E5" s="1">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>4.99</v>
+        <v>13.35</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
@@ -721,25 +727,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
-        <v>5.25</v>
+        <v>14.5</v>
       </c>
       <c r="D6" s="1">
-        <v>4.99</v>
+        <v>14.21</v>
       </c>
       <c r="E6" s="1">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1">
-        <v>4.99</v>
+        <v>14.21</v>
       </c>
       <c r="H6" t="s">
         <v>10</v>
@@ -747,10 +753,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1">
         <v>5.25</v>
@@ -762,7 +768,7 @@
         <v>0.26</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
         <v>4.99</v>
@@ -788,7 +794,7 @@
         <v>0.26</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
         <v>4.99</v>
@@ -814,7 +820,7 @@
         <v>0.26</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
         <v>4.99</v>
@@ -840,7 +846,7 @@
         <v>0.26</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1">
         <v>4.99</v>
@@ -866,7 +872,7 @@
         <v>0.26</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1">
         <v>4.99</v>
@@ -892,7 +898,7 @@
         <v>0.26</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
@@ -918,7 +924,7 @@
         <v>0.26</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
@@ -944,7 +950,7 @@
         <v>0.26</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
@@ -970,7 +976,7 @@
         <v>0.26</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
@@ -996,7 +1002,7 @@
         <v>0.26</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
@@ -1022,7 +1028,7 @@
         <v>0.26</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
@@ -1048,7 +1054,7 @@
         <v>0.26</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
@@ -1074,7 +1080,7 @@
         <v>0.26</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
@@ -1100,7 +1106,7 @@
         <v>0.26</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
@@ -1126,7 +1132,7 @@
         <v>0.26</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
@@ -1152,7 +1158,7 @@
         <v>0.26</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
@@ -1178,7 +1184,7 @@
         <v>0.26</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
@@ -1195,19 +1201,19 @@
         <v>34</v>
       </c>
       <c r="C24" s="1">
-        <v>12.25</v>
+        <v>5.25</v>
       </c>
       <c r="D24" s="1">
-        <v>12.06</v>
+        <v>4.99</v>
       </c>
       <c r="E24" s="1">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G24" s="1">
-        <v>12.06</v>
+        <v>4.99</v>
       </c>
       <c r="H24" t="s">
         <v>10</v>
@@ -1221,19 +1227,19 @@
         <v>35</v>
       </c>
       <c r="C25" s="1">
-        <v>13.75</v>
+        <v>5.25</v>
       </c>
       <c r="D25" s="1">
-        <v>13.56</v>
+        <v>4.99</v>
       </c>
       <c r="E25" s="1">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="F25" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G25" s="1">
-        <v>13.56</v>
+        <v>4.99</v>
       </c>
       <c r="H25" t="s">
         <v>10</v>
@@ -1247,19 +1253,19 @@
         <v>36</v>
       </c>
       <c r="C26" s="1">
-        <v>9.99</v>
+        <v>12.25</v>
       </c>
       <c r="D26" s="1">
-        <v>9.95</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="F26" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G26" s="1">
-        <v>9.95</v>
+        <v>12</v>
       </c>
       <c r="H26" t="s">
         <v>10</v>
@@ -1267,25 +1273,25 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" s="1">
-        <v>9.99</v>
+        <v>12.69</v>
       </c>
       <c r="D27" s="1">
-        <v>9.95</v>
+        <v>12.47</v>
       </c>
       <c r="E27" s="1">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G27" s="1">
-        <v>9.95</v>
+        <v>12.47</v>
       </c>
       <c r="H27" t="s">
         <v>10</v>
@@ -1293,10 +1299,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="1">
         <v>9.99</v>
@@ -1308,7 +1314,7 @@
         <v>0.04</v>
       </c>
       <c r="F28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G28" s="1">
         <v>9.95</v>
@@ -1334,7 +1340,7 @@
         <v>0.04</v>
       </c>
       <c r="F29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G29" s="1">
         <v>9.95</v>
@@ -1360,7 +1366,7 @@
         <v>0.04</v>
       </c>
       <c r="F30" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G30" s="1">
         <v>9.95</v>
@@ -1386,7 +1392,7 @@
         <v>0.04</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G31" s="1">
         <v>9.95</v>
@@ -1412,7 +1418,7 @@
         <v>0.04</v>
       </c>
       <c r="F32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G32" s="1">
         <v>9.95</v>
@@ -1438,7 +1444,7 @@
         <v>0.04</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G33" s="1">
         <v>9.95</v>
@@ -1464,7 +1470,7 @@
         <v>0.04</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G34" s="1">
         <v>9.95</v>
@@ -1490,7 +1496,7 @@
         <v>0.04</v>
       </c>
       <c r="F35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G35" s="1">
         <v>9.95</v>
@@ -1516,7 +1522,7 @@
         <v>0.04</v>
       </c>
       <c r="F36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G36" s="1">
         <v>9.95</v>
@@ -1542,7 +1548,7 @@
         <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G37" s="1">
         <v>9.95</v>
@@ -1568,7 +1574,7 @@
         <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G38" s="1">
         <v>9.95</v>
@@ -1594,7 +1600,7 @@
         <v>0.04</v>
       </c>
       <c r="F39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G39" s="1">
         <v>9.95</v>
@@ -1620,7 +1626,7 @@
         <v>0.04</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G40" s="1">
         <v>9.95</v>
@@ -1646,7 +1652,7 @@
         <v>0.04</v>
       </c>
       <c r="F41" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G41" s="1">
         <v>9.95</v>
@@ -1672,7 +1678,7 @@
         <v>0.04</v>
       </c>
       <c r="F42" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G42" s="1">
         <v>9.95</v>
@@ -1698,7 +1704,7 @@
         <v>0.04</v>
       </c>
       <c r="F43" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G43" s="1">
         <v>9.95</v>
@@ -1724,7 +1730,7 @@
         <v>0.04</v>
       </c>
       <c r="F44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G44" s="1">
         <v>9.95</v>
@@ -1750,7 +1756,7 @@
         <v>0.04</v>
       </c>
       <c r="F45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G45" s="1">
         <v>9.95</v>
@@ -1776,12 +1782,64 @@
         <v>0.04</v>
       </c>
       <c r="F46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G46" s="1">
         <v>9.95</v>
       </c>
       <c r="H46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D47" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F47" t="s">
+        <v>39</v>
+      </c>
+      <c r="G47" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="D48" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="F48" t="s">
+        <v>39</v>
+      </c>
+      <c r="G48" s="1">
+        <v>9.95</v>
+      </c>
+      <c r="H48" t="s">
         <v>10</v>
       </c>
     </row>
